--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2020_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2020_metropolitana.xlsx
@@ -186,7 +186,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:35</t>
+    <t xml:space="preserve">2026-09-09 20:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_rezmat_a_2020_metropolitana.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_rezmat_a_2020_metropolitana.xlsx
@@ -24,159 +24,159 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
+    <t xml:space="preserve">Santiago</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerrillos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cerro Navia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conchalí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Bosque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Huechuraba</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cisterna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Florida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Granja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Pintana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Reina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Las Condes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Barnechea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Espejo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lo Prado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Macul</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maipú</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ñuñoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedro Aguirre Cerda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peñalolén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Providencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pudahuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilicura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinta Normal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recoleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Renca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Joaquín</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Miguel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Ramón</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitacura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puente Alto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pirque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San José de Maipo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lampa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tiltil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Bernardo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calera de Tango</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melipilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alhué</t>
   </si>
   <si>
-    <t xml:space="preserve">Buin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calera de Tango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerrillos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerro Navia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Colina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conchalí</t>
-  </si>
-  <si>
     <t xml:space="preserve">Curacaví</t>
   </si>
   <si>
-    <t xml:space="preserve">El Bosque</t>
+    <t xml:space="preserve">María Pinto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talagante</t>
   </si>
   <si>
     <t xml:space="preserve">El Monte</t>
   </si>
   <si>
-    <t xml:space="preserve">Huechuraba</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Independencia</t>
-  </si>
-  <si>
     <t xml:space="preserve">Isla de Maipo</t>
   </si>
   <si>
-    <t xml:space="preserve">La Cisterna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Florida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Granja</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Pintana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Reina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lampa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Las Condes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Barnechea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Espejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lo Prado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Macul</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maipú</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Pinto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melipilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ñuñoa</t>
-  </si>
-  <si>
     <t xml:space="preserve">Padre Hurtado</t>
   </si>
   <si>
-    <t xml:space="preserve">Paine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pedro Aguirre Cerda</t>
-  </si>
-  <si>
     <t xml:space="preserve">Peñaflor</t>
   </si>
   <si>
-    <t xml:space="preserve">Peñalolén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pirque</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Providencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pudahuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puente Alto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilicura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quinta Normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recoleta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Renca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Bernardo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Joaquín</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San José de Maipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Miguel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Pedro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Ramón</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santiago</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talagante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tiltil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitacura</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -186,7 +186,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:37</t>
+    <t xml:space="preserve">2026-09-18 10:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -598,7 +598,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.15</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="3">
@@ -606,7 +606,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.99</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="4">
@@ -614,7 +614,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.78</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="5">
@@ -622,7 +622,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5.51</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="6">
@@ -630,7 +630,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>5.98</v>
+        <v>5.79</v>
       </c>
     </row>
     <row r="7">
@@ -638,7 +638,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>4.41</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="8">
@@ -646,7 +646,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6.21</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="9">
@@ -654,7 +654,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="10">
@@ -662,7 +662,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.79</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="11">
@@ -670,7 +670,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4.63</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="12">
@@ -678,7 +678,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>4.27</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="13">
@@ -686,7 +686,7 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>3.79</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="14">
@@ -694,7 +694,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>5.2</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="15">
@@ -702,7 +702,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3.8</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="16">
@@ -710,7 +710,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4.57</v>
+        <v>6.55</v>
       </c>
     </row>
     <row r="17">
@@ -718,7 +718,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5.83</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="18">
@@ -726,7 +726,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>7.32</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="19">
@@ -734,7 +734,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2.89</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="20">
@@ -742,7 +742,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>4.97</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="21">
@@ -750,7 +750,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2.02</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="22">
@@ -758,7 +758,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>2.58</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="23">
@@ -766,7 +766,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>6.55</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="24">
@@ -774,7 +774,7 @@
         <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>5.85</v>
+        <v>4.45</v>
       </c>
     </row>
     <row r="25">
@@ -782,7 +782,7 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>4.91</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="26">
@@ -790,7 +790,7 @@
         <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4.52</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="27">
@@ -798,7 +798,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>3.38</v>
+        <v>5.48</v>
       </c>
     </row>
     <row r="28">
@@ -806,7 +806,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>4.26</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="29">
@@ -814,7 +814,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>2.26</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="30">
@@ -822,7 +822,7 @@
         <v>30</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>4.33</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="31">
@@ -830,7 +830,7 @@
         <v>31</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>4.81</v>
+        <v>6.74</v>
       </c>
     </row>
     <row r="32">
@@ -838,7 +838,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>5.47</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="33">
@@ -846,7 +846,7 @@
         <v>33</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>3.86</v>
+        <v>5.57</v>
       </c>
     </row>
     <row r="34">
@@ -854,7 +854,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>5.01</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="35">
@@ -862,7 +862,7 @@
         <v>35</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>3.44</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="36">
@@ -870,7 +870,7 @@
         <v>36</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>1.56</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="37">
@@ -878,7 +878,7 @@
         <v>37</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>4.45</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="38">
@@ -886,7 +886,7 @@
         <v>38</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>5.57</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="39">
@@ -894,7 +894,7 @@
         <v>39</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>4.73</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="40">
@@ -902,7 +902,7 @@
         <v>40</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>4.49</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="41">
@@ -910,7 +910,7 @@
         <v>41</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>5.48</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="42">
@@ -918,7 +918,7 @@
         <v>42</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>5.4</v>
+        <v>4.81</v>
       </c>
     </row>
     <row r="43">
@@ -926,7 +926,7 @@
         <v>43</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>4.93</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="44">
@@ -934,7 +934,7 @@
         <v>44</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="45">
@@ -942,7 +942,7 @@
         <v>45</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>5.05</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="46">
@@ -950,7 +950,7 @@
         <v>46</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="47">
@@ -966,7 +966,7 @@
         <v>48</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>6.74</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="49">
@@ -974,7 +974,7 @@
         <v>49</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>3.81</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="50">
@@ -982,7 +982,7 @@
         <v>50</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>4.04</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="51">
@@ -990,7 +990,7 @@
         <v>51</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>3.69</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="52">
@@ -998,7 +998,7 @@
         <v>52</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>1.08</v>
+        <v>3.86</v>
       </c>
     </row>
   </sheetData>
